--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -1310,6 +1310,11 @@
       <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Deepseek</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Gemini-3.5-Flash-Lite (OR)</t>
         </is>
       </c>
     </row>
@@ -1344,6 +1349,9 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" t="n">
+        <v>0.6429</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1363,6 +1371,9 @@
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="n"/>
+      <c r="H4" t="n">
+        <v>0.7143</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1382,6 +1393,9 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" t="n">
+        <v>0.5373</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1401,6 +1415,9 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1433,6 +1450,9 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="n"/>
+      <c r="H8" t="n">
+        <v>0.74</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1452,6 +1472,9 @@
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" t="n">
+        <v>0.745</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1472,6 +1495,10 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="n"/>
+      <c r="H10">
+        <f>AVERAGE(H6,H9)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1514,149 +1541,149 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Splits</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>XAI</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Gemma</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Deepseek</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>capability</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>mission_explicit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>mission_implicit</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>mission_open-ended</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>mission</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <f>AVERAGE(B3:B5)</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <f>AVERAGE(C3:C5)</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <f>AVERAGE(D3:D5)</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <f>AVERAGE(E3:E5)</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <f>AVERAGE(F3:F5)</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <f>AVERAGE(G3:G5)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>emotion</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>culture</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>perspective (2nd-order)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>Overall Score</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <f>AVERAGE(B2,B6,B7,B8,B9)</f>
         <v/>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <f>AVERAGE(C2,C6,C7,C8,C9)</f>
         <v/>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <f>AVERAGE(D2,D6,D7,D8,D9)</f>
         <v/>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <f>AVERAGE(E2,E6,E7,E8,E9)</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <f>AVERAGE(F2,F6,F7,F8,F9)</f>
         <v/>
       </c>
-      <c r="G10">
+      <c r="G10" s="0">
         <f>AVERAGE(G2,G6,G7,G8,G9)</f>
         <v/>
       </c>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -1284,35 +1284,30 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>XAI</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Gemma</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
           <t>Deepseek</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Gemini-3.5-Flash-Lite (OR)</t>
         </is>
@@ -1327,9 +1322,8 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1337,19 +1331,14 @@
           <t>emotional_cues</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>0.464</v>
       </c>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" t="n">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="0" t="n">
         <v>0.6429</v>
       </c>
     </row>
@@ -1359,19 +1348,14 @@
           <t>personal_beliefs_and_experiences</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="B4" s="2" t="n">
         <v>0.2</v>
       </c>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" t="n">
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="0" t="n">
         <v>0.7143</v>
       </c>
     </row>
@@ -1381,19 +1365,14 @@
           <t>perspective_taking</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
+      <c r="B5" s="2" t="n">
         <v>0.647</v>
       </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" t="n">
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="0" t="n">
         <v>0.5373</v>
       </c>
     </row>
@@ -1403,19 +1382,14 @@
           <t>eu_overall</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>0.5</v>
       </c>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" t="n">
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="0" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -1428,9 +1402,8 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1438,19 +1411,14 @@
           <t>Personal-Self</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
+      <c r="B8" s="2" t="n">
         <v>0.74</v>
       </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" t="n">
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="0" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -1460,19 +1428,14 @@
           <t>ea_overall</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
+      <c r="B9" s="2" t="n">
         <v>0.74</v>
       </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" t="n">
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="0" t="n">
         <v>0.745</v>
       </c>
     </row>
@@ -1482,21 +1445,16 @@
           <t>Overall</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C10" s="2">
-        <f>AVERAGE(C6,C9)</f>
-        <v/>
-      </c>
+      <c r="B10" s="2">
+        <f>AVERAGE(B6,B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10">
-        <f>AVERAGE(H6,H9)</f>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="0">
+        <f>AVERAGE(G6,G9)</f>
         <v/>
       </c>
     </row>
@@ -1505,26 +1463,23 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="2" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="2" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -1310,6 +1310,11 @@
       <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Gemini-3.5-Flash-Lite (OR)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>GPT-5.6-Luna (effort=medium)</t>
         </is>
       </c>
     </row>
@@ -1326,160 +1331,234 @@
       <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>emotional_cues</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="0" t="n">
-        <v>0.6429</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>complex_emotions</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7347</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>personal_beliefs_and_experiences</t>
+          <t>emotional_cues</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2</v>
+        <v>0.464</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="0" t="n">
-        <v>0.7143</v>
+        <v>0.6429</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>perspective_taking</t>
+          <t>personal_beliefs_and_experiences</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.647</v>
+        <v>0.2</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="0" t="n">
-        <v>0.5373</v>
+        <v>0.7143</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6786</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>eu_overall</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>perspective_taking</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.647</v>
       </c>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="0" t="n">
-        <v>0.65</v>
+        <v>0.5373</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5373</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Emotional Application (EA)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>eu_overall</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.5</v>
+      </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="2" t="n"/>
+      <c r="G7" s="0" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.675</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Personal-Self</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0.74</v>
-      </c>
+          <t>Emotional Application (EA)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="0" t="n">
-        <v>0.74</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>ea_overall</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="0" t="n">
-        <v>0.745</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Personal-Others</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <f>AVERAGE(B6,B9)</f>
-        <v/>
+          <t>Personal-Self</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.74</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="0">
-        <f>AVERAGE(G6,G9)</f>
-        <v/>
+      <c r="G10" s="0" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Social-Others</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Social-Self</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.76</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ea_overall</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.74</v>
+      </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="2" t="n"/>
+      <c r="G13" s="0" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.745</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <f>AVERAGE(B7,B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="0">
+        <f>AVERAGE(G7,G13)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>AVERAGE(H7,H13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -2,12 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="Big Bench Hard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="MMLU" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DocVQA" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Emo" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Awareness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Provenance" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,68 +21,71 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color theme="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="FF000000"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDE5F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="1">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -150,56 +158,114 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -211,189 +277,238 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35.13" customWidth="1" style="6" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Splits</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>XAI</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gemma</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deepseek</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kimi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Llama</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>boolean_expressions</t>
         </is>
@@ -410,13 +525,15 @@
       <c r="E2" s="2" t="n">
         <v>0.992</v>
       </c>
-      <c r="F2" s="3" t="n"/>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>causal_judgement</t>
         </is>
@@ -433,13 +550,15 @@
       <c r="E3" s="2" t="n">
         <v>0.615</v>
       </c>
-      <c r="F3" s="3" t="n"/>
+      <c r="F3" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G3" s="2" t="n">
         <v>0.679</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>date_understanding</t>
         </is>
@@ -456,13 +575,15 @@
       <c r="E4" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="3" t="n"/>
+      <c r="F4" s="2" t="n">
+        <v>0.9360000000000001</v>
+      </c>
       <c r="G4" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>dyck_languages</t>
         </is>
@@ -479,13 +600,15 @@
       <c r="E5" s="2" t="n">
         <v>0.416</v>
       </c>
-      <c r="F5" s="3" t="n"/>
+      <c r="F5" s="2" t="n">
+        <v>0.828</v>
+      </c>
       <c r="G5" s="2" t="n">
         <v>0.836</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>formal_fallacies</t>
         </is>
@@ -502,13 +625,15 @@
       <c r="E6" s="2" t="n">
         <v>0.952</v>
       </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="F6" s="2" t="n">
+        <v>0.912</v>
+      </c>
       <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>geometric_shapes</t>
         </is>
@@ -525,13 +650,15 @@
       <c r="E7" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="2" t="n">
+        <v>0.648</v>
+      </c>
       <c r="G7" s="2" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>logical_deduction_five_objects</t>
         </is>
@@ -548,13 +675,15 @@
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="3" t="n"/>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="n">
         <v>0.984</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>logical_deduction_seven_objects</t>
         </is>
@@ -571,13 +700,15 @@
       <c r="E9" s="2" t="n">
         <v>0.992</v>
       </c>
-      <c r="F9" s="3" t="n"/>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="n">
         <v>0.992</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>logical_deduction_three_objects</t>
         </is>
@@ -594,13 +725,15 @@
       <c r="E10" s="2" t="n">
         <v>0.996</v>
       </c>
-      <c r="F10" s="3" t="n"/>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G10" s="2" t="n">
         <v>0.992</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>multistep_arithmetic_two</t>
         </is>
@@ -617,13 +750,15 @@
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="3" t="n"/>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="n">
         <v>0.996</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>navigate</t>
         </is>
@@ -640,13 +775,15 @@
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="3" t="n"/>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>object_counting</t>
         </is>
@@ -663,13 +800,15 @@
       <c r="E13" s="2" t="n">
         <v>0.992</v>
       </c>
-      <c r="F13" s="3" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="n">
         <v>0.996</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>penguins_in_a_table</t>
         </is>
@@ -686,13 +825,15 @@
       <c r="E14" s="2" t="n">
         <v>0.9320000000000001</v>
       </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>reasoning_about_colored_objects</t>
         </is>
@@ -709,13 +850,15 @@
       <c r="E15" s="2" t="n">
         <v>0.952</v>
       </c>
-      <c r="F15" s="3" t="n"/>
+      <c r="F15" s="2" t="n">
+        <v>0.988</v>
+      </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>temporal_sequences</t>
         </is>
@@ -732,13 +875,15 @@
       <c r="E16" s="2" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="F16" s="3" t="n"/>
+      <c r="F16" s="2" t="n">
+        <v>0.984</v>
+      </c>
       <c r="G16" s="2" t="n">
         <v>0.996</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>tracking_shuffled_objects_five_objects</t>
         </is>
@@ -755,13 +900,15 @@
       <c r="E17" s="2" t="n">
         <v>0.988</v>
       </c>
-      <c r="F17" s="3" t="n"/>
+      <c r="F17" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tracking_shuffled_objects_seven_objects</t>
         </is>
@@ -778,13 +925,15 @@
       <c r="E18" s="2" t="n">
         <v>0.868</v>
       </c>
-      <c r="F18" s="3" t="n"/>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>tracking_shuffled_objects_three_objects</t>
         </is>
@@ -801,13 +950,15 @@
       <c r="E19" s="2" t="n">
         <v>0.908</v>
       </c>
-      <c r="F19" s="3" t="n"/>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>web_of_lies</t>
         </is>
@@ -824,13 +975,15 @@
       <c r="E20" s="2" t="n">
         <v>0.916</v>
       </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>word_sorting</t>
         </is>
@@ -847,7 +1000,9 @@
       <c r="E21" s="2" t="n">
         <v>0.86</v>
       </c>
-      <c r="F21" s="3" t="n"/>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
@@ -855,30 +1010,29 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Overall Score</t>
-        </is>
-      </c>
-      <c r="B22" s="3">
-        <f>AVERAGE(B2:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="3">
-        <f>AVERAGE(C2:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="3">
-        <f>AVERAGE(D2:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="3">
-        <f>AVERAGE(E2:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3">
-        <f>AVERAGE(G2:G21)</f>
-        <v/>
-      </c>
+          <t>Overall Score (macro-avg of 20 tasks)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0.9122</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0.8337</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.9401</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.9008</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.9493</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -888,44 +1042,66 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21.63" customWidth="1" style="6" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Splits</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>XAI</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Gemma</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deepseek</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Llama</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Business_ethics</t>
         </is>
@@ -939,12 +1115,15 @@
       <c r="D2" s="2" t="n">
         <v>0.82</v>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>0.82</v>
+      </c>
       <c r="G2" s="2" t="n">
         <v>0.83</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Econometrics</t>
         </is>
@@ -958,12 +1137,15 @@
       <c r="D3" s="2" t="n">
         <v>0.8159999999999999</v>
       </c>
+      <c r="F3" s="2" t="n">
+        <v>0.842</v>
+      </c>
       <c r="G3" s="2" t="n">
         <v>0.904</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Elementary_math</t>
         </is>
@@ -977,12 +1159,15 @@
       <c r="D4" s="2" t="n">
         <v>0.979</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>0.984</v>
+      </c>
       <c r="G4" s="2" t="n">
         <v>0.981</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Formal_logic</t>
         </is>
@@ -1001,7 +1186,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Jurisprudence</t>
         </is>
@@ -1015,12 +1200,15 @@
       <c r="D6" s="2" t="n">
         <v>0.898</v>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>0.88</v>
+      </c>
       <c r="G6" s="2" t="n">
         <v>0.889</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Logical_fallacies</t>
         </is>
@@ -1034,12 +1222,15 @@
       <c r="D7" s="2" t="n">
         <v>0.902</v>
       </c>
+      <c r="F7" s="2" t="n">
+        <v>0.902</v>
+      </c>
       <c r="G7" s="2" t="n">
         <v>0.902</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Management</t>
         </is>
@@ -1053,12 +1244,15 @@
       <c r="D8" s="2" t="n">
         <v>0.903</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>0.913</v>
+      </c>
       <c r="G8" s="2" t="n">
         <v>0.903</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
@@ -1072,12 +1266,15 @@
       <c r="D9" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="F9" s="2" t="n">
+        <v>0.953</v>
+      </c>
       <c r="G9" s="2" t="n">
         <v>0.97</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Miscellaneous</t>
         </is>
@@ -1096,7 +1293,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Moral_disputes</t>
         </is>
@@ -1110,12 +1307,15 @@
       <c r="D11" s="2" t="n">
         <v>0.855</v>
       </c>
+      <c r="F11" s="2" t="n">
+        <v>0.835</v>
+      </c>
       <c r="G11" s="2" t="n">
         <v>0.855</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Moral_scenarios</t>
         </is>
@@ -1134,7 +1334,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Philosophy</t>
         </is>
@@ -1153,7 +1353,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Professional_accounting</t>
         </is>
@@ -1172,27 +1372,26 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Overall Score</t>
-        </is>
-      </c>
-      <c r="B15" s="5">
-        <f>AVERAGE(B2:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="5">
-        <f>AVERAGE(C2:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="5">
-        <f>AVERAGE(D2:D14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="5">
-        <f>AVERAGE(G1:G14)</f>
-        <v/>
-      </c>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Overall Score (macro-avg of 13 tasks)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0.8812</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.8011</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.9018</v>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="4" t="n">
+        <v>0.9174</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1202,65 +1401,97 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Splits</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>XAI</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gemma</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deepseek</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Overall accuracy</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>0.9491493737147131</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0.8745559917741634</v>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="4" t="n">
+        <v>0.9611142269583099</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0.930641241353524</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ANLS</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.9357379949597689</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.8582502323174737</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.9567989102943297</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9293253169272407</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1270,65 +1501,84 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Splits</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>XAI</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gemma</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deepseek</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>Gemini-3.5-Flash-Lite (OR)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Gemini-3.5-Flash-Lite (OpenRouter)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>GPT-5.6-Luna (effort=medium)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Emotional Understanding (EU)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1336,104 +1586,169 @@
           <t>complex_emotions</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="B3" s="2" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.6122</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.8163</v>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>0.7347</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" s="2" t="n">
         <v>0.8163</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>emotional_cues</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="0" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.4643</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>0.6429</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" s="2" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>personal_beliefs_and_experiences</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="0" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.6964</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.6607</v>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>0.7143</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" s="2" t="n">
         <v>0.6786</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>perspective_taking</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="0" t="n">
+        <v>0.5671641791044776</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>0.5373</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" s="2" t="n">
         <v>0.5373</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>eu_overall</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="0" t="n">
+      <c r="B7" s="4" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" s="4" t="n">
         <v>0.675</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Emotional Application (EA)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1441,30 +1756,59 @@
           <t>Personal-Others</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="B9" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>0.78</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Personal-Self</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>0.74</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="0" t="n">
+      <c r="D10" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>0.74</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" s="2" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1474,10 +1818,28 @@
           <t>Social-Others</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="B11" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>0.76</v>
       </c>
-      <c r="H11" t="n">
+      <c r="G11" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -1487,78 +1849,92 @@
           <t>Social-Self</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="B12" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H12" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" s="2" t="n">
         <v>0.76</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>ea_overall</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="0" t="n">
+      <c r="B13" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>0.745</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" s="4" t="n">
         <v>0.745</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="B14" s="2">
-        <f>AVERAGE(B7,B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="0">
-        <f>AVERAGE(G7,G13)</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>AVERAGE(H7,H13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Overall Score</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.6725</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.71</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1573,153 +1949,593 @@
   </sheetPr>
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Splits</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>XAI</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gemma</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Deepseek</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>capability</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>mission_explicit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>mission_implicit</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>mission_open-ended</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>mission</t>
         </is>
       </c>
-      <c r="B6" s="0">
-        <f>AVERAGE(B3:B5)</f>
-        <v/>
-      </c>
-      <c r="C6" s="0">
-        <f>AVERAGE(C3:C5)</f>
-        <v/>
-      </c>
-      <c r="D6" s="0">
-        <f>AVERAGE(D3:D5)</f>
-        <v/>
-      </c>
-      <c r="E6" s="0">
-        <f>AVERAGE(E3:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="0">
-        <f>AVERAGE(F3:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="0">
-        <f>AVERAGE(G3:G5)</f>
-        <v/>
-      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>emotion</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>culture</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>perspective (2nd-order)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Overall Score</t>
         </is>
       </c>
-      <c r="B10" s="0">
-        <f>AVERAGE(B2,B6,B7,B8,B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="0">
-        <f>AVERAGE(C2,C6,C7,C8,C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="0">
-        <f>AVERAGE(D2,D6,D7,D8,D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="0">
-        <f>AVERAGE(E2,E6,E7,E8,E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="0">
-        <f>AVERAGE(F2,F6,F7,F8,F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="0">
-        <f>AVERAGE(G2,G6,G7,G8,G9)</f>
-        <v/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Results.xlsx — Every model that has appeared in an experiment. Rebuilt 2026-08-29 from the result files on disk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Big Bench Hard</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Gemini · OpenAI · XAI · Qwen · Deepseek</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>carried unchanged from the 2026-08-26 Results.xlsx</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>NOT bbh/&lt;m&gt;/&lt;m&gt;_overall_results.csv — those hold a strict-scorer partial re-run and disagree (gemini date_understanding 0.064 there vs 0.936 here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Big Bench Hard</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Gemma</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>bbh/gemma/gemma_overall_results.csv</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>NEW — the run is complete and healthy: 20 tasks, 4,833 rows, empty errlog, and every per-task CSV mean equals the overall CSV. Its 12 perfect tasks are real; spot-checked rows show the lenient matcher crediting correct answers a strict scorer would zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Big Bench Hard</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>READ THIS BEFORE RANKING</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>two scorers in one sheet</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>XAI, Gemma and Qwen are scored by a six-branch lenient matcher; Gemini, OpenAI and Deepseek by case-folded string equality. The strict three are penalised for formatting, not reasoning, so a gap in this row is not purely ability. Tasks_benchmarks/bbh/README.md has the six branches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Big Bench Hard</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Kimi · Llama (Results.xlsx only)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>blank column = the run happened, no comparable number</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>kimi has 1 task, llama_overall_results.csv is empty; both strict-scorer, not comparable to the columns beside them</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>MMLU</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Gemini · OpenAI · Deepseek</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Tasks_benchmarks/mmlu/&lt;m&gt;_overall_results.csv</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>matches the previous workbook exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>MMLU</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>XAI</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Tasks_benchmarks/mmlu/xai/xai_overall_results.csv</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>matches the previous workbook exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>MMLU</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Gemma</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Tasks_benchmarks/mmlu/gemma/gemma_overall_results.csv</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>NEW — 8 of 13 subjects only; the other 5 were never written</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>MMLU</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>qwen_overall_results.csv exists but is empty; per-subject qwen_*.csv are unscored</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MMLU</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Llama (Results.xlsx only)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>blank column = the run happened, no number</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>mmlu/llama/llama_overall_results.csv is empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Gemini · OpenAI</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>&lt;m&gt;_docvqa_overall.csv</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>qwen_DocVQA/qwen_docvqa_overall.csv</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>NEW — was on disk, never entered the workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Gemma</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>gemma_DocVQA/gemma_docvqa_overall_half{1,2}.csv</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>NEW — two halves recombined weighted by rows: (2320+2658)/(2500+2849)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>XAI · Deepseek</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>no DocVQA run on disk</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>OpenAI · XAI · Qwen · Gemma · Deepseek</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>EmoBench/emobench_results.csv</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>REPLACES the previous column — the old OpenAI values pre-dated the shard-overwrite fix (eu_overall was 0.5, is 0.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>EMO_Gemini_Flash2.5/results/{EU,EA}/gemini-2_5-flash_en_overall.csv</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>NEW — the run completed but is missing from emobench_results.csv; EMO_SCRIPT.md section 6 lists it</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>the two extras (Results.xlsx only)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>EmoBench/emobench_results.csv</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>ran on EmoBench, not among the six</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>all six</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>no model has been scored yet; awareness_results.csv holds only the paper baselines</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Overall Score</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>BBH · MMLU</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>computed here</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>unweighted macro-average over the tasks, written only when every task in the sheet has a value</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Overall Score</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>emobench_results.csv Overall_Score</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>mean of EA_Overall and EU_Overall, as defined by the source</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +57,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +88,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -446,18 +461,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,223 +522,245 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>boolean_expressions</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Model / config</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash ⚠ superseded</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>grok-3-mini</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>deepseek-reasoner</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>kimi-k2.5</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-4-Maverick-17B-128E-Instruct-FP8</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>causal_judgement</t>
+          <t>boolean_expressions</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.636</v>
+        <v>0.984</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.642</v>
+        <v>0.976</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.642</v>
+        <v>0.996</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.615</v>
+        <v>0.992</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.679</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date_understanding</t>
+          <t>causal_judgement</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.642</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.642</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.615</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dyck_languages</t>
+          <t>date_understanding</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.732</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.376</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.752</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.416</v>
+        <v>0.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.828</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.836</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>formal_fallacies</t>
+          <t>dyck_languages</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.988</v>
+        <v>0.732</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.376</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.996</v>
+        <v>0.752</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.952</v>
+        <v>0.416</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.912</v>
+        <v>0.828</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>geometric_shapes</t>
+          <t>formal_fallacies</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.824</v>
+        <v>0.988</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.768</v>
+        <v>0.996</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8</v>
+        <v>0.952</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.648</v>
+        <v>0.912</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>logical_deduction_five_objects</t>
+          <t>geometric_shapes</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.972</v>
+        <v>0.824</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.876</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0.768</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>0.648</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.984</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>logical_deduction_seven_objects</t>
+          <t>logical_deduction_five_objects</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.98</v>
+        <v>0.972</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.876</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.992</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>logical_deduction_three_objects</t>
+          <t>logical_deduction_seven_objects</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.996</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -735,42 +772,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>multistep_arithmetic_two</t>
+          <t>logical_deduction_three_objects</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.584</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.98</v>
+        <v>0.996</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>0.996</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>navigate</t>
+          <t>multistep_arithmetic_two</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.984</v>
+        <v>0.584</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.952</v>
+        <v>0.98</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
@@ -779,79 +816,79 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>object_counting</t>
+          <t>navigate</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.92</v>
+        <v>0.984</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.924</v>
+        <v>0.952</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>penguins_in_a_table</t>
+          <t>object_counting</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.993</v>
+        <v>0.924</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.992</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reasoning_about_colored_objects</t>
+          <t>penguins_in_a_table</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.92</v>
+        <v>0.993</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.952</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -860,70 +897,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>temporal_sequences</t>
+          <t>reasoning_about_colored_objects</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>0.988</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.956</v>
+        <v>0.92</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.992</v>
+        <v>0.988</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.952</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.984</v>
+        <v>0.988</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tracking_shuffled_objects_five_objects</t>
+          <t>temporal_sequences</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>0.988</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.952</v>
+        <v>0.956</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.988</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tracking_shuffled_objects_seven_objects</t>
+          <t>tracking_shuffled_objects_five_objects</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.952</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.868</v>
+        <v>0.988</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
@@ -935,20 +972,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tracking_shuffled_objects_three_objects</t>
+          <t>tracking_shuffled_objects_seven_objects</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.984</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.908</v>
+        <v>0.868</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
@@ -960,20 +997,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>web_of_lies</t>
+          <t>tracking_shuffled_objects_three_objects</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.716</v>
+        <v>0.984</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.944</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.916</v>
+        <v>0.908</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
@@ -985,54 +1022,79 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>web_of_lies</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>word_sorting</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>0.868</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C22" s="2" t="n">
         <v>0.492</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D22" s="2" t="n">
         <v>0.908</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E22" s="2" t="n">
         <v>0.86</v>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Overall Score (macro-avg of 20 tasks)</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B23" s="4" t="n">
         <v>0.9122</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C23" s="4" t="n">
         <v>0.8337</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.9401</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>0.9008</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>0.9493</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0.9605</v>
       </c>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1045,17 +1107,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,298 +1162,340 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Business_ethics</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.83</v>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Model / config</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash ⚠ superseded</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>grok-3-mini</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>deepseek-reasoner</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-4-Maverick-17B-128E-Instruct-FP8</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Econometrics</t>
+          <t>Business_ethics</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.588</v>
+        <v>0.78</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.842</v>
+        <v>0.82</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.904</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elementary_math</t>
+          <t>Econometrics</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.929</v>
+        <v>0.86</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.958</v>
+        <v>0.588</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.979</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.984</v>
+        <v>0.842</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.981</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Formal_logic</t>
+          <t>Elementary_math</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.929</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.643</v>
+        <v>0.958</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.976</v>
+        <v>0.979</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.984</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.976</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jurisprudence</t>
+          <t>Formal_logic</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.907</v>
+        <v>0.96</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.843</v>
+        <v>0.643</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.976</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.889</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Logical_fallacies</t>
+          <t>Jurisprudence</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.877</v>
+        <v>0.907</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.828</v>
+        <v>0.843</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.902</v>
+        <v>0.898</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.902</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.902</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Logical_fallacies</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.877</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.835</v>
+        <v>0.828</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.913</v>
+        <v>0.902</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.949</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.835</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.903</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.953</v>
+        <v>0.913</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.97</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>0.949</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.911</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.968</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.953</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.958</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moral_disputes</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.844</v>
+        <v>0.949</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.806</v>
+        <v>0.911</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.835</v>
+        <v>0.968</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.855</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moral_scenarios</t>
+          <t>Moral_disputes</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.842</v>
+        <v>0.844</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.708</v>
+        <v>0.806</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.849</v>
+        <v>0.855</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.835</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.869</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Philosophy</t>
+          <t>Moral_scenarios</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.881</v>
+        <v>0.842</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.797</v>
+        <v>0.708</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.881</v>
+        <v>0.849</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.91</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Philosophy</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Professional_accounting</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>0.745</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>0.777</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D15" s="2" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.979</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Overall Score (macro-avg of 13 tasks)</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B16" s="4" t="n">
         <v>0.8812</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.8011</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.9018</v>
       </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="4" t="n">
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="4" t="n">
         <v>0.9174</v>
       </c>
-      <c r="H15" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1404,16 +1508,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1453,43 +1557,80 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Model / config</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash ⚠ superseded</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Overall accuracy</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B3" s="4" t="n">
         <v>0.9491493737147131</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C3" s="4" t="n">
         <v>0.8745559917741634</v>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="4" t="n">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="4" t="n">
         <v>0.9611142269583099</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.930641241353524</v>
       </c>
-      <c r="G2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>ANLS</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B4" s="2" t="n">
         <v>0.9357379949597689</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C4" s="2" t="n">
         <v>0.8582502323174737</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>0.9567989102943297</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.9293253169272407</v>
       </c>
     </row>
@@ -1504,18 +1645,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
-    <col width="31" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1556,384 +1697,431 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Gemini-3.5-Flash-Lite (OpenRouter)</t>
+          <t>Gemini-2.5-Flash</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>GPT-5.6-Luna (effort=medium)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+          <t>GPT-4o-mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Model / config</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash-lite · OpenRouter, effort=minimal ✓ settled</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-5.6-luna · effort=medium ⚠ settled is low</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>grok-3-mini</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>deepseek-reasoner</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash ⚠ superseded</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Emotional Understanding (EU)</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>complex_emotions</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.8367346938775511</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.6122</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.6735</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.8163</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.7347</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.8163</v>
-      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>emotional_cues</t>
+          <t>complex_emotions</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7347</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.4643</v>
+        <v>0.8163</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8571</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.6735</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8571</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8163</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6429</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.6122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>personal_beliefs_and_experiences</t>
+          <t>emotional_cues</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0.4107</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.7321</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.6964</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.6607</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.7143</v>
-      </c>
       <c r="I5" s="2" t="n">
-        <v>0.6786</v>
+        <v>0.4643</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>personal_beliefs_and_experiences</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.6786</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.6964</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.6607</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.4107</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>perspective_taking</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>0.5671641791044776</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>0.3582</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>0.6418</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.4478</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.6269</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.6119</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.5373</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0.5373</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>eu_overall</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>0.695</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="H8" s="4" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.675</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Emotional Application (EA)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Personal-Others</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Personal-Self</t>
+          <t>Personal-Others</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>0.78</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="F10" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>0.82</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.74</v>
-      </c>
       <c r="I10" s="2" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Social-Others</t>
+          <t>Personal-Self</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>0.68</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.78</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.76</v>
-      </c>
       <c r="I11" s="2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Social-Others</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Social-Self</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B13" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>0.66</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>0.66</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>ea_overall</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0.745</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Overall Score</t>
+          <t>ea_overall</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.715</v>
+        <v>0.745</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.575</v>
+        <v>0.745</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>0.735</v>
       </c>
       <c r="E14" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Overall Score</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>0.635</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>0.745</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.6725</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>0.6975</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0.71</v>
+      <c r="H15" s="4" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.575</v>
       </c>
     </row>
   </sheetData>
@@ -1947,16 +2135,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1996,80 +2184,117 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>capability</t>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Model / config</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mission_explicit</t>
+          <t>capability</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mission_implicit</t>
+          <t>mission_explicit</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>mission_implicit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>mission_open-ended</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>mission</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>emotion</t>
-        </is>
-      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>emotion</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>perspective (2nd-order)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Overall Score</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2085,10 +2310,10 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2121,68 +2346,68 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Big Bench Hard</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Gemini · OpenAI · XAI · Qwen · Deepseek</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>carried unchanged from the 2026-08-26 Results.xlsx</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>NOT bbh/&lt;m&gt;/&lt;m&gt;_overall_results.csv — those hold a strict-scorer partial re-run and disagree (gemini date_understanding 0.064 there vs 0.936 here)</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>READ FIRST</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>row 2 of every sheet</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>the runners</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Row 2 names the model and config that produced each column. A column header is a SLOT, not a model — two slots hold a different model on Emo than on the other sheets.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Big Bench Hard</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Gemma</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>bbh/gemma/gemma_overall_results.csv</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>NEW — the run is complete and healthy: 20 tasks, 4,833 rows, empty errlog, and every per-task CSV mean equals the overall CSV. Its 12 perfect tasks are real; spot-checked rows show the lenient matcher crediting correct answers a strict scorer would zero.</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>READ FIRST</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Gemini and OpenAI slots</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>PLAN.md, "The six, by name"</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>The six were re-pointed: the Gemini slot is gemini-3.5-flash-lite and the OpenAI slot is gpt-5.6-luna. Only Emo has been run on them. bbh, MMLU and DocVQA still hold gemini-2.5-flash and gpt-4o-mini-2024-07-18 because those runners were never re-pointed — the numbers are real, they are just the superseded models. Re-pointing means re-running, not editing a header.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Big Bench Hard</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>READ THIS BEFORE RANKING</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>two scorers in one sheet</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>XAI, Gemma and Qwen are scored by a six-branch lenient matcher; Gemini, OpenAI and Deepseek by case-folded string equality. The strict three are penalised for formatting, not reasoning, so a gap in this row is not purely ability. Tasks_benchmarks/bbh/README.md has the six branches.</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>READ FIRST</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Big Bench Hard, all columns</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Tasks_benchmarks/bbh/README.md</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>That sheet mixes two scorers. XAI, Gemma and Qwen use a six-branch lenient matcher; Gemini, OpenAI and Deepseek use case-folded string equality and are penalised for formatting, not reasoning. Do not rank the row without this.</t>
         </is>
       </c>
     </row>
@@ -2194,61 +2419,61 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Kimi · Llama (Results.xlsx only)</t>
+          <t>Gemini · OpenAI · XAI · Qwen · Deepseek</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>blank column = the run happened, no comparable number</t>
+          <t>carried from the 2026-08-26 workbook</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>kimi has 1 task, llama_overall_results.csv is empty; both strict-scorer, not comparable to the columns beside them</t>
+          <t>NOT from &lt;model&gt;_overall_results.csv — those hold a later degraded re-run (gemini date_understanding 0.064 there vs 0.936 here).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI · Deepseek</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Tasks_benchmarks/mmlu/&lt;m&gt;_overall_results.csv</t>
+          <t>BBH_Gemma overall CSV, 2026-08-29</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>matches the previous workbook exactly</t>
+          <t>Run verified complete: 20 tasks, 4,833 rows, empty errlog, per-task CSV means equal to the overall CSV.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>XAI</t>
+          <t>Kimi · Llama (Results.xlsx only)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Tasks_benchmarks/mmlu/xai/xai_overall_results.csv</t>
+          <t>blank column = the run happened, no comparable number</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>matches the previous workbook exactly</t>
+          <t>kimi has 1 task, llama none; both strict-scored partial re-runs.</t>
         </is>
       </c>
     </row>
@@ -2260,17 +2485,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Gemini · OpenAI · XAI · Deepseek</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Tasks_benchmarks/mmlu/gemma/gemma_overall_results.csv</t>
+          <t>mmlu &lt;model&gt;_overall_results.csv</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>NEW — 8 of 13 subjects only; the other 5 were never written</t>
+          <t>unchanged; matches the previous workbook.</t>
         </is>
       </c>
     </row>
@@ -2282,17 +2507,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>mmlu/gemma/gemma_overall_results.csv</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>qwen_overall_results.csv exists but is empty; per-subject qwen_*.csv are unscored</t>
+          <t>8 of 13 subjects; the other five were never written.</t>
         </is>
       </c>
     </row>
@@ -2304,17 +2529,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Llama (Results.xlsx only)</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>blank column = the run happened, no number</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>mmlu/llama/llama_overall_results.csv is empty</t>
+          <t>qwen_overall_results.csv exists but is empty.</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2556,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>&lt;m&gt;_docvqa_overall.csv</t>
+          <t>&lt;model&gt;_docvqa_overall.csv</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>unchanged.</t>
         </is>
       </c>
     </row>
@@ -2348,17 +2573,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>Qwen · Gemma</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>qwen_DocVQA/qwen_docvqa_overall.csv</t>
+          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>NEW — was on disk, never entered the workbook</t>
+          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
         </is>
       </c>
     </row>
@@ -2370,39 +2595,39 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>gemma_DocVQA/gemma_docvqa_overall_half{1,2}.csv</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>NEW — two halves recombined weighted by rows: (2320+2658)/(2500+2849)</t>
+          <t>no DocVQA run exists.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>Emo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>Gemini = gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>no DocVQA run on disk</t>
+          <t>The settled config: OpenRouter, reasoning effort minimal (REASONING_EFFORT in the runner). This is the selected model, in its slot.</t>
         </is>
       </c>
     </row>
@@ -2414,17 +2639,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OpenAI · XAI · Qwen · Gemma · Deepseek</t>
+          <t>OpenAI = gpt-5.6-luna</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>EmoBench/emobench_results.csv</t>
+          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>REPLACES the previous column — the old OpenAI values pre-dated the shard-overwrite fix (eu_overall was 0.5, is 0.45)</t>
+          <t>ONLY THE DEFAULT (medium) ARM IS COMPLETE. The settled config is reasoning_effort="low", and results_eLow has EU (0.650) but no EA, so no complete score exists at the settled config. Closing this means one EA run at effort=low.</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2661,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>XAI · Qwen · Gemma · Deepseek</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EMO_Gemini_Flash2.5/results/{EU,EA}/gemini-2_5-flash_en_overall.csv</t>
+          <t>EmoBench/emobench_results.csv</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>NEW — the run completed but is missing from emobench_results.csv; EMO_SCRIPT.md section 6 lists it</t>
+          <t>unchanged.</t>
         </is>
       </c>
     </row>
@@ -2458,17 +2683,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>the two extras (Results.xlsx only)</t>
+          <t>the two superseded (Results.xlsx only)</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>EmoBench/emobench_results.csv</t>
+          <t>emobench_results.csv; EMO_Gemini_Flash2.5/results for the Gemini</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>ran on EmoBench, not among the six</t>
+          <t>gemini-2.5-flash and gpt-4o-mini kept as their own columns — they held the Gemini and OpenAI slots before the re-point and their Emo numbers are real.</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2715,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>no model has been scored yet; awareness_results.csv holds only the paper baselines</t>
+          <t>no model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2727,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>BBH · MMLU</t>
+          <t>bbh · MMLU</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -2512,7 +2737,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>unweighted macro-average over the tasks, written only when every task in the sheet has a value</t>
+          <t>unweighted macro-average, written only where every task in the sheet has a value.</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2759,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>mean of EA_Overall and EU_Overall, as defined by the source</t>
+          <t>mean of EA_Overall and EU_Overall, as the source defines it.</t>
         </is>
       </c>
     </row>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Model / config</t>
@@ -530,12 +530,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash ⚠ superseded</t>
+          <t>gemini-2.5-flash</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+          <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Model / config</t>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash ⚠ superseded</t>
+          <t>gemini-2.5-flash</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+          <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Model / config</t>
@@ -1565,17 +1565,17 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash ⚠ superseded</t>
+          <t>gemini-2.5-flash</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+          <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>grok-3-mini</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>deepseek-reasoner</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Model / config</t>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite · OpenRouter, effort=minimal ✓ settled</t>
+          <t>gemini-3.5-flash-lite (OpenRouter, minimal)</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna · effort=medium ⚠ settled is low</t>
+          <t>gpt-5.6-luna (effort=medium)</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash ⚠ superseded</t>
+          <t>gemini-2.5-flash</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>gpt-4o-mini-2024-07-18 ⚠ superseded</t>
+          <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Model / config</t>
@@ -2192,32 +2192,32 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>gpt-5.6-luna</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>grok-3-mini</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>Qwen/Qwen3.5-9B</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>google/gemma-4-31B-it</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>deepseek-reasoner</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2353,17 +2353,17 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>row 2 of every sheet</t>
+          <t>what this workbook is</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>the runners</t>
+          <t>every model that has appeared in an experiment</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Row 2 names the model and config that produced each column. A column header is a SLOT, not a model — two slots hold a different model on Emo than on the other sheets.</t>
+          <t>Including models that were tried and dropped, and the two that were replaced. Row 2 of each sheet names the model and config behind each column.</t>
         </is>
       </c>
     </row>
@@ -2375,39 +2375,39 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Gemini and OpenAI slots</t>
+          <t>Gemini and OpenAI columns</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>PLAN.md, "The six, by name"</t>
+          <t>the model differs by sheet</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>The six were re-pointed: the Gemini slot is gemini-3.5-flash-lite and the OpenAI slot is gpt-5.6-luna. Only Emo has been run on them. bbh, MMLU and DocVQA still hold gemini-2.5-flash and gpt-4o-mini-2024-07-18 because those runners were never re-pointed — the numbers are real, they are just the superseded models. Re-pointing means re-running, not editing a header.</t>
+          <t>A header is a slot, not a model. On bbh, MMLU and DocVQA those slots hold gemini-2.5-flash and gpt-4o-mini-2024-07-18, which is what their runners call. On Emo they hold the current pair, gemini-3.5-flash-lite and gpt-5.6-luna, and the superseded pair keeps its own two columns beside them.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>READ FIRST</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Big Bench Hard, all columns</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Tasks_benchmarks/bbh/README.md</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>That sheet mixes two scorers. XAI, Gemma and Qwen use a six-branch lenient matcher; Gemini, OpenAI and Deepseek use case-folded string equality and are penalised for formatting, not reasoning. Do not rank the row without this.</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Big Bench Hard</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Gemini · OpenAI</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>carried from the 2026-08-26 workbook</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash and gpt-4o-mini-2024-07-18. Both are strict-scored — see the two-scorer row below.</t>
         </is>
       </c>
     </row>
@@ -2419,178 +2419,178 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI · XAI · Qwen · Deepseek</t>
+          <t>Kimi · Llama</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>carried from the 2026-08-26 workbook</t>
+          <t>blank column = the run happened, no comparable number</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>NOT from &lt;model&gt;_overall_results.csv — those hold a later degraded re-run (gemini date_understanding 0.064 there vs 0.936 here).</t>
+          <t>kimi completed 1 task, llama none; both are strict-scored partial re-runs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Big Bench Hard</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Gemini · OpenAI</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>BBH_Gemma overall CSV, 2026-08-29</t>
+          <t>mmlu &lt;model&gt;_overall_results.csv</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Run verified complete: 20 tasks, 4,833 rows, empty errlog, per-task CSV means equal to the overall CSV.</t>
+          <t>gemini-2.5-flash and gpt-4o-mini-2024-07-18.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Big Bench Hard</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kimi · Llama (Results.xlsx only)</t>
+          <t>Llama</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>blank column = the run happened, no comparable number</t>
+          <t>blank column = the run happened, no number</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>kimi has 1 task, llama none; both strict-scored partial re-runs.</t>
+          <t>llama_overall_results.csv is empty.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI · XAI · Deepseek</t>
+          <t>Gemini · OpenAI</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>mmlu &lt;model&gt;_overall_results.csv</t>
+          <t>&lt;model&gt;_docvqa_overall.csv</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>unchanged; matches the previous workbook.</t>
+          <t>gemini-2.5-flash and gpt-4o-mini-2024-07-18.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Emo</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Gemini-2.5-Flash · GPT-4o-mini</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>mmlu/gemma/gemma_overall_results.csv</t>
+          <t>emobench_results.csv; EMO_Gemini_Flash2.5/results for the Gemini</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>8 of 13 subjects; the other five were never written.</t>
+          <t>The pair that held the two slots before the re-point. Their EmoBench numbers are real results of models that are no longer selected.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>all columns</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>Tasks_benchmarks/bbh/README.md</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>qwen_overall_results.csv exists but is empty.</t>
+          <t>This sheet mixes two scorers. XAI, Gemma and Qwen use a six-branch lenient matcher; Deepseek uses case-folded string equality and is penalised for formatting, not reasoning. Do not rank the row without this.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI</t>
+          <t>XAI · Qwen · Deepseek</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>&lt;model&gt;_docvqa_overall.csv</t>
+          <t>carried from the 2026-08-26 workbook</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>unchanged.</t>
+          <t>NOT from &lt;model&gt;_overall_results.csv — those hold a later degraded re-run (gemini date_understanding 0.064 there vs 0.936 in the workbook).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Qwen · Gemma</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
+          <t>BBH_Gemma overall CSV, 2026-08-29</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
+          <t>Verified complete: 20 tasks, 4,833 rows, empty errlog, per-task CSV means equal to the overall CSV.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -2600,166 +2600,232 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>mmlu &lt;model&gt;_overall_results.csv</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>no DocVQA run exists.</t>
+          <t>Matches the previous workbook.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Gemini = gemini-3.5-flash-lite</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
+          <t>mmlu/gemma/gemma_overall_results.csv</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>The settled config: OpenRouter, reasoning effort minimal (REASONING_EFFORT in the runner). This is the selected model, in its slot.</t>
+          <t>8 of 13 subjects; the other five were never written.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OpenAI = gpt-5.6-luna</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>ONLY THE DEFAULT (medium) ARM IS COMPLETE. The settled config is reasoning_effort="low", and results_eLow has EU (0.650) but no EA, so no complete score exists at the settled config. Closing this means one EA run at effort=low.</t>
+          <t>qwen_overall_results.csv exists but is empty.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>XAI · Qwen · Gemma · Deepseek</t>
+          <t>Qwen · Gemma</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EmoBench/emobench_results.csv</t>
+          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>unchanged.</t>
+          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>the two superseded (Results.xlsx only)</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>emobench_results.csv; EMO_Gemini_Flash2.5/results for the Gemini</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash and gpt-4o-mini kept as their own columns — they held the Gemini and OpenAI slots before the re-point and their Emo numbers are real.</t>
+          <t>no DocVQA run exists.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Emo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>all six</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>no model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
+          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Overall Score</t>
+          <t>Emo</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>bbh · MMLU</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>computed here</t>
+          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>unweighted macro-average, written only where every task in the sheet has a value.</t>
+          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>XAI · Qwen · Gemma · Deepseek</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>EmoBench/emobench_results.csv</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>every column</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>Overall Score</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>bbh · MMLU</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>computed here</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Unweighted macro-average, written only where every task in the sheet has a value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Overall Score</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Emo</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>emobench_results.csv Overall_Score</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>mean of EA_Overall and EU_Overall, as the source defines it.</t>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Mean of EA_Overall and EU_Overall, as the source defines it.</t>
         </is>
       </c>
     </row>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -471,8 +471,10 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,10 +515,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Gemini-2.5-Flash</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>GPT-4o-mini</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Kimi</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Llama</t>
         </is>
@@ -530,40 +542,50 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
+          <t>gemini-3.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>grok-3-mini</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>deepseek-reasoner</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
           <t>gemini-2.5-flash</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>grok-3-mini</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Qwen/Qwen3.5-9B</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>google/gemma-4-31B-it</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>kimi-k2.5</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>meta-llama/Llama-4-Maverick-17B-128E-Instruct-FP8</t>
         </is>
@@ -576,10 +598,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.976</v>
+        <v>0.996</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.996</v>
@@ -593,6 +612,18 @@
       <c r="G3" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,23 +631,29 @@
           <t>causal_judgement</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.642</v>
-      </c>
       <c r="D4" s="2" t="n">
-        <v>0.642</v>
+        <v>0.6417</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.615</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6898</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.679</v>
+        <v>0.6791</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.6417</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.6738</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.6631</v>
       </c>
     </row>
     <row r="5">
@@ -625,12 +662,6 @@
           <t>date_understanding</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>0.9360000000000001</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.8159999999999999</v>
-      </c>
       <c r="D5" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
@@ -643,6 +674,18 @@
       <c r="G5" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.928</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -650,14 +693,8 @@
           <t>dyck_languages</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0.376</v>
-      </c>
       <c r="D6" s="2" t="n">
-        <v>0.752</v>
+        <v>0.756</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.416</v>
@@ -668,6 +705,18 @@
       <c r="G6" s="2" t="n">
         <v>0.836</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -675,17 +724,11 @@
           <t>formal_fallacies</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0.8159999999999999</v>
-      </c>
       <c r="D7" s="2" t="n">
         <v>0.996</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.952</v>
+        <v>0.968</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.912</v>
@@ -693,6 +736,15 @@
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H7" s="2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.852</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -700,12 +752,6 @@
           <t>geometric_shapes</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>0.824</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="D8" s="2" t="n">
         <v>0.768</v>
       </c>
@@ -718,6 +764,18 @@
       <c r="G8" s="2" t="n">
         <v>0.8</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.632</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -725,12 +783,6 @@
           <t>logical_deduction_five_objects</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0.876</v>
-      </c>
       <c r="D9" s="2" t="n">
         <v>1</v>
       </c>
@@ -743,6 +795,18 @@
       <c r="G9" s="2" t="n">
         <v>0.984</v>
       </c>
+      <c r="H9" s="2" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.972</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -750,12 +814,6 @@
           <t>logical_deduction_seven_objects</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.8159999999999999</v>
-      </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
@@ -768,6 +826,18 @@
       <c r="G10" s="2" t="n">
         <v>0.992</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.912</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,12 +845,6 @@
           <t>logical_deduction_three_objects</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.996</v>
-      </c>
       <c r="D11" s="2" t="n">
         <v>1</v>
       </c>
@@ -793,6 +857,18 @@
       <c r="G11" s="2" t="n">
         <v>0.992</v>
       </c>
+      <c r="H11" s="2" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -800,12 +876,6 @@
           <t>multistep_arithmetic_two</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0.98</v>
-      </c>
       <c r="D12" s="2" t="n">
         <v>0.996</v>
       </c>
@@ -818,6 +888,15 @@
       <c r="G12" s="2" t="n">
         <v>0.996</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -825,23 +904,26 @@
           <t>navigate</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>0.984</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0.952</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -850,12 +932,6 @@
           <t>object_counting</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0.924</v>
-      </c>
       <c r="D14" s="2" t="n">
         <v>0.88</v>
       </c>
@@ -868,6 +944,15 @@
       <c r="G14" s="2" t="n">
         <v>0.996</v>
       </c>
+      <c r="H14" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.984</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -875,23 +960,26 @@
           <t>penguins_in_a_table</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0.993</v>
-      </c>
       <c r="D15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9315</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.9795</v>
       </c>
     </row>
     <row r="16">
@@ -900,12 +988,6 @@
           <t>reasoning_about_colored_objects</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>0.92</v>
-      </c>
       <c r="D16" s="2" t="n">
         <v>0.988</v>
       </c>
@@ -918,6 +1000,18 @@
       <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H16" s="2" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.948</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -925,12 +1019,6 @@
           <t>temporal_sequences</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0.956</v>
-      </c>
       <c r="D17" s="2" t="n">
         <v>0.992</v>
       </c>
@@ -943,6 +1031,18 @@
       <c r="G17" s="2" t="n">
         <v>0.996</v>
       </c>
+      <c r="H17" s="2" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.988</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -950,12 +1050,6 @@
           <t>tracking_shuffled_objects_five_objects</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0.952</v>
-      </c>
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
@@ -968,6 +1062,15 @@
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H18" s="2" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -975,12 +1078,6 @@
           <t>tracking_shuffled_objects_seven_objects</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0.9320000000000001</v>
-      </c>
       <c r="D19" s="2" t="n">
         <v>1</v>
       </c>
@@ -993,6 +1090,15 @@
       <c r="G19" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H19" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.964</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1000,12 +1106,6 @@
           <t>tracking_shuffled_objects_three_objects</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0.984</v>
-      </c>
       <c r="D20" s="2" t="n">
         <v>1</v>
       </c>
@@ -1018,6 +1118,15 @@
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H20" s="2" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1025,12 +1134,6 @@
           <t>web_of_lies</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0.716</v>
-      </c>
       <c r="D21" s="2" t="n">
         <v>0.944</v>
       </c>
@@ -1043,6 +1146,15 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.888</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1050,12 +1162,6 @@
           <t>word_sorting</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0.492</v>
-      </c>
       <c r="D22" s="2" t="n">
         <v>0.908</v>
       </c>
@@ -1068,6 +1174,15 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H22" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.904</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1075,26 +1190,30 @@
           <t>Overall Score (macro-avg of 20 tasks)</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0.9122</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0.8337</v>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="4" t="n">
-        <v>0.9401</v>
+        <v>0.9403</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9008</v>
+        <v>0.9015</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0.9493</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.9605</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
+        <v>0.9606</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.8337</v>
+      </c>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="4" t="n">
+        <v>0.9109</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2307,7 +2426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2363,7 +2482,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Including models that were tried and dropped, and the two that were replaced. Row 2 of each sheet names the model and config behind each column.</t>
+          <t>Including models tried and dropped, and the two that were replaced. Row 2 of each sheet names the model and config behind each column.</t>
         </is>
       </c>
     </row>
@@ -2375,17 +2494,17 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Gemini and OpenAI columns</t>
+          <t>Gemini and OpenAI slots</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>the model differs by sheet</t>
+          <t>the current pair, everywhere</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>A header is a slot, not a model. On bbh, MMLU and DocVQA those slots hold gemini-2.5-flash and gpt-4o-mini-2024-07-18, which is what their runners call. On Emo they hold the current pair, gemini-3.5-flash-lite and gpt-5.6-luna, and the superseded pair keeps its own two columns beside them.</t>
+          <t>The Gemini and OpenAI slots hold gemini-3.5-flash-lite and gpt-5.6-luna on every sheet. The models they replaced, gemini-2.5-flash and gpt-4o-mini-2024-07-18, keep columns of their own on bbh and Emo. On MMLU and DocVQA only the superseded pair has run, so those slots are theirs for now — row 2 says which.</t>
         </is>
       </c>
     </row>
@@ -2397,17 +2516,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI</t>
+          <t>every column</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>carried from the 2026-08-26 workbook</t>
+          <t>Tasks_benchmarks/bbh/BBH_*/results/*_bbh_overall.csv</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash and gpt-4o-mini-2024-07-18. Both are strict-scored — see the two-scorer row below.</t>
+          <t>Refreshed 2026-08-29 from the uniform rescore, scorer tag lenient_v2: every model scored by the same six-branch matcher out of bbh_eval_core.py. The sheet is now reproducible from one source, and the old strict-vs-lenient caveat no longer applies here.</t>
         </is>
       </c>
     </row>
@@ -2419,227 +2538,227 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Kimi · Llama</t>
+          <t>Gemini = gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>blank column = the run happened, no comparable number</t>
+          <t>1 of 20 tasks — run in progress</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>kimi completed 1 task, llama none; both are strict-scored partial re-runs.</t>
+          <t>The selected Gemini has started on bbh. Only the tasks it has finished carry a value; Overall Score stays blank until all 20 are in.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI</t>
+          <t>OpenAI = gpt-5.6-luna</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>mmlu &lt;model&gt;_overall_results.csv</t>
+          <t>blank — not yet run</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash and gpt-4o-mini-2024-07-18.</t>
+          <t>BBH_GPT_5.6_Luna has a runner but no results.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Llama</t>
+          <t>Overall Score</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>blank column = the run happened, no number</t>
+          <t>macro-average over the 20 tasks</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>llama_overall_results.csv is empty.</t>
+          <t>Written only for a column with all 20, so the row stays comparable. Kimi has 10 tasks and a 10-task macro of 0.8938, which is deliberately not put in a row labelled 20.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Gemini · OpenAI</t>
+          <t>Gemini-2.5-Flash</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>&lt;model&gt;_docvqa_overall.csv</t>
+          <t>BBH_Gemini_Flash2.5, macro 0.3387</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash and gpt-4o-mini-2024-07-18.</t>
+          <t>A BROKEN RUN, kept as a record. 3,002 of its 4,833 responses never emitted "Final Answer:", so no scorer can rescue them — the lenient matcher has nothing to match. This replaces the 0.9122 the workbook carried until 2026-08-29, whose source run is not on disk. The model is superseded, so it will not be redone.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Gemini-2.5-Flash · GPT-4o-mini</t>
+          <t>GPT-4o-mini · Kimi · Llama</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>emobench_results.csv; EMO_Gemini_Flash2.5/results for the Gemini</t>
+          <t>their BBH_* overall CSVs</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>The pair that held the two slots before the re-point. Their EmoBench numbers are real results of models that are no longer selected.</t>
+          <t>gpt-4o-mini 0.8337 (superseded), llama 0.9109, kimi 10 tasks. Kimi and Llama were never among the six; the rescore gave them real numbers where this workbook previously had empty columns.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Big Bench Hard</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>all columns</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Tasks_benchmarks/bbh/README.md</t>
+          <t>mmlu &lt;model&gt;_overall_results.csv</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>This sheet mixes two scorers. XAI, Gemma and Qwen use a six-branch lenient matcher; Deepseek uses case-folded string equality and is penalised for formatting, not reasoning. Do not rank the row without this.</t>
+          <t>Matches the previous workbook.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Big Bench Hard</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>XAI · Qwen · Deepseek</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>carried from the 2026-08-26 workbook</t>
+          <t>mmlu/gemma/gemma_overall_results.csv</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>NOT from &lt;model&gt;_overall_results.csv — those hold a later degraded re-run (gemini date_understanding 0.064 there vs 0.936 in the workbook).</t>
+          <t>8 of 13 subjects; the other five were never written.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Big Bench Hard</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>BBH_Gemma overall CSV, 2026-08-29</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Verified complete: 20 tasks, 4,833 rows, empty errlog, per-task CSV means equal to the overall CSV.</t>
+          <t>qwen_overall_results.csv exists but is empty.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>MMLU · DocVQA</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>scoring</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>mmlu &lt;model&gt;_overall_results.csv</t>
+          <t>still per-runner</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Matches the previous workbook.</t>
+          <t>Only bbh has been moved onto one shared lenient matcher. Until MMLU and DocVQA follow, their columns are not guaranteed to be scored the same way as each other.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Qwen · Gemma</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>mmlu/gemma/gemma_overall_results.csv</t>
+          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>8 of 13 subjects; the other five were never written.</t>
+          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2649,51 +2768,51 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>qwen_overall_results.csv exists but is empty.</t>
+          <t>No DocVQA run exists.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>Emo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Qwen · Gemma</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
+          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
+          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>Emo</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>no DocVQA run exists.</t>
+          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
         </is>
       </c>
     </row>
@@ -2705,127 +2824,39 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>XAI · Qwen · Gemma · Deepseek</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
+          <t>EmoBench/emobench_results.csv</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
+          <t>Unchanged.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>every column</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Emo</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>XAI · Qwen · Gemma · Deepseek</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>EmoBench/emobench_results.csv</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>every column</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
           <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Overall Score</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>bbh · MMLU</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>computed here</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Unweighted macro-average, written only where every task in the sheet has a value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Overall Score</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Emo</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>emobench_results.csv Overall_Score</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Mean of EA_Overall and EU_Overall, as the source defines it.</t>
         </is>
       </c>
     </row>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1470,7 +1470,7 @@
           <t>Business_ethics</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
@@ -1501,7 +1501,7 @@
           <t>Econometrics</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
         <v>0.8683999999999999</v>
       </c>
       <c r="C4" s="2" t="n">
@@ -1532,8 +1532,8 @@
           <t>Elementary_math</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>0.9841</v>
+      <c r="B5" t="n">
+        <v>0.9815</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.9841</v>
@@ -1563,8 +1563,8 @@
           <t>Formal_logic</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>0.9365</v>
+      <c r="B6" t="n">
+        <v>0.9762</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.9683</v>
@@ -1594,8 +1594,8 @@
           <t>Jurisprudence</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>0.9352</v>
+      <c r="B7" t="n">
+        <v>0.9074</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.9258999999999999</v>
@@ -1625,8 +1625,8 @@
           <t>Logical_fallacies</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>0.908</v>
+      <c r="B8" t="n">
+        <v>0.9202</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.9202</v>
@@ -1656,8 +1656,8 @@
           <t>Management</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>0.8932</v>
+      <c r="B9" t="n">
+        <v>0.8835</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.9223</v>
@@ -1687,8 +1687,8 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>0.9701</v>
+      <c r="B10" t="n">
+        <v>0.9573</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.9658</v>
@@ -1718,8 +1718,8 @@
           <t>Miscellaneous</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>0.9745</v>
+      <c r="B11" t="n">
+        <v>0.9757</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0.9745</v>
@@ -1749,7 +1749,7 @@
           <t>Moral_disputes</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" t="n">
         <v>0.8584000000000001</v>
       </c>
       <c r="C12" s="2" t="n">
@@ -1780,7 +1780,7 @@
           <t>Moral_scenarios</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" t="n">
         <v>0.8514</v>
       </c>
       <c r="C13" s="2" t="n">
@@ -1811,7 +1811,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="n">
         <v>0.91</v>
       </c>
       <c r="C14" s="2" t="n">
@@ -1842,7 +1842,7 @@
           <t>Professional_accounting</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" t="n">
         <v>0.9752</v>
       </c>
       <c r="C15" s="2" t="n">
@@ -1873,7 +1873,7 @@
           <t>Overall Score (macro-avg of 13 tasks)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="3" t="n">
         <v>0.9135</v>
       </c>
       <c r="C16" s="4" t="n">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>13 of 13 subjects — two routes</t>
+          <t>13 of 13 subjects — one route</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>MMLU_Gemini_Flash3.5lite_Google, 3,943 rows, macro 0.9135, 0 empty, 1 no_marker. TWO ROUTES IN ONE COLUMN: 1,755 rows were answered by OpenRouter on 2026-08-30 before its balance ran out (HTTP 402, limit_source openrouter_credits) and 2,188 by Google AI Studio on 2026-09-07; every row's config column names which. MMLU_Gemini_Flash3.5lite_OpenRouter/ is kept untouched as the record of that first run, 2,188 of whose rows are empty.</t>
+          <t>MMLU_Gemini_Flash3.5lite_Google, 3,943 rows, macro 0.9135, 0 empty, 0 no_marker, ONE ROUTE. The folder began as a copy of the OpenRouter run so its 1,755 answered rows would not be paid for twice; on 2026-09-07 the user decided to redo them here as well, so those rows were pruned and re-asked and every row now carries route=google_aistudio, thinking_budget=128, seed=42. MMLU_Gemini_Flash3.5lite_OpenRouter/ keeps the original run, 2,188 of whose rows are empty after its balance ran out (HTTP 402); it is a record, not a result.</t>
         </is>
       </c>
     </row>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>blank — text-only models, not an unrun benchmark</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>No DocVQA run exists.</t>
+          <t>Neither model can take an image, so this is a ceiling and not an outstanding run: DocVQA is document VQA and the runners send image bytes. Read from each provider's model metadata on 2026-09-08 — deepseek-reasoner is text-only (DeepSeek's one vision model is deepseek-v4-flash-vision-exp), and grok-3-mini can no longer be asked because xAI has retired it. Filling these two means changing the model, which is a decision about the six.</t>
         </is>
       </c>
     </row>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1909,7 +1909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1957,6 +1957,16 @@
           <t>Deepseek</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Gemini-2.5-Flash</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>GPT-4o-mini</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -1966,32 +1976,42 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
+          <t>gemini-3.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>grok-3-mini</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>deepseek-reasoner</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>gemini-2.5-flash</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>gpt-4o-mini-2024-07-18</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>grok-3-mini</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Qwen/Qwen3.5-9B</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>google/gemma-4-31B-it</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
         </is>
       </c>
     </row>
@@ -2002,19 +2022,25 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.9491493737147131</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.8745559917741634</v>
+        <v>0.9151</v>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="4" t="n">
-        <v>0.9611142269583099</v>
+        <v>0.9611</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.930641241353524</v>
+        <v>0.9306</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8746</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2023,16 +2049,22 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9357379949597689</v>
+        <v>0.9394</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.8582502323174737</v>
+        <v>0.8635</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9567989102943297</v>
+        <v>0.9568</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9293253169272407</v>
+        <v>0.9293</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9357</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8583</v>
       </c>
     </row>
   </sheetData>
@@ -2708,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3036,7 +3068,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MMLU · DocVQA</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3051,29 +3083,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Two scorers on this sheet. Gemini and OpenAI are scored by mmlu_eval_core.score_response (mmlu_lenient_v1), the one lenient matcher; the other columns carry the score their own runner wrote with ==. A uniform rescore of the seven older slots has not been run, so a small cross-model difference here may be the scorer rather than the model. DocVQA is still per-runner throughout.</t>
+          <t>Two scorers on the MMLU sheet. Gemini and OpenAI are scored by mmlu_eval_core.score_response (mmlu_lenient_v1), the one lenient matcher; the other MMLU columns carry the score their own runner wrote with ==. A uniform rescore of those seven older slots has not been run, so a small cross-model difference on that sheet may be the scorer rather than the model. bbh and DocVQA do not have this problem: bbh is uniformly lenient_v5, and DocVQA's shared core carries a verbatim copy of what its four standalone runners each used, so all of its columns are judged alike.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DocVQA</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Qwen · Gemma</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>every column</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tasks_benchmarks/DocVQA/**/&lt;model&gt;_docvqa_results.csv and DOCVQA_*/results/&lt;slug&gt;.jsonl</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Refreshed 2026-09-10 from the per-row result files, not from any roll-up. Every column is the full 5,349 validation questions. Scorer docvqa_anls_v1 — one matcher for all six: the two runners added 2026-09-10 import it from docvqa_eval_core.py, and it is a verbatim copy of what the four earlier standalone runners each carried, so the columns are comparable. ANLS takes the max over each question's answer list, threshold 0.5.</t>
         </is>
       </c>
     </row>
@@ -3085,103 +3117,191 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>Gemini = gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>blank — text-only models, not an unrun benchmark</t>
+          <t>5,349 rows — 5 unanswerable</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Neither model can take an image, so this is a ceiling and not an outstanding run: DocVQA is document VQA and the runners send image bytes. Read from each provider's model metadata on 2026-09-08 — deepseek-reasoner is text-only (DeepSeek's one vision model is deepseek-v4-flash-vision-exp), and grok-3-mini can no longer be asked because xAI has retired it. Filling these two means changing the model, which is a decision about the six.</t>
+          <t>DOCVQA_Gemini_Flash3.5lite_Google, 5,349 rows, accuracy 0.9602, ANLS 0.9394. Native Google AI Studio route, thinking_budget=128, max_output_tokens=8192, seed=42 — the same config as its MMLU column. FIVE ROWS ARE PERMANENTLY EMPTY: finish_reason MALFORMED_RESPONSE, thought tokens spent and no output part, reproducible at the same seed. They are scored 0. 5 of 5,349 is 0.09%.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>OpenAI = gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>5,349 rows — complete</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>DOCVQA_GPT_5.6_Luna, 5,349 rows, accuracy 0.9151, ANLS 0.8635, 0 empty. max_completion_tokens=16384, reasoning_effort=low, seed=42 — the same config as its MMLU and bbh columns. Run as 5 shards with a 2.5 s sleep, which is the fix from the daily-cap incident in OPENAI_EVAL_NOTES.md, not a preference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Qwen · Gemma</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5,349 rows each — complete</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Qwen 5,349 rows, 3 empty. Gemma is two halves recombined and recomputed over all 5,349 rows rather than averaged: 2,500 + 2,849, 16 empty between them. Both predate the shared core and carry their own copy of the same matcher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gemini-2.5-Flash · GPT-4o-mini</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5,349 rows each — superseded</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash 0.9491/0.9357 (3 empty) and gpt-4o-mini 0.8746/0.8583 (0 empty). Both complete, both superseded, kept as their own columns rather than filling the slots their replacements now hold. Note OPENAI_EVAL_NOTES.md describes an earlier gpt-4o-mini run that left 3,021 rows empty; the file on disk is the repaired one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DocVQA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XAI · Deepseek</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>blank — text-only models, not an unrun benchmark</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Neither model can take an image, so this is a ceiling and not an outstanding run: DocVQA is document VQA and the runners send image bytes. Read from each provider's model metadata on 2026-09-08 — deepseek-reasoner is text-only, and grok-3-mini can no longer be asked because xAI has retired it. Filling these two means changing the model, which is a decision about the six.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>Emo</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Emo</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Emo</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>XAI · Qwen · Gemma · Deepseek</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>EmoBench/emobench_results.csv</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Unchanged.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Awareness</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>every column</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
         </is>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -2022,24 +2022,24 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9686</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.9151</v>
+        <v>0.9288</v>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="4" t="n">
-        <v>0.9611</v>
+        <v>0.9705</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.9306</v>
+        <v>0.9405</v>
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9587</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8746</v>
+        <v>0.8841</v>
       </c>
     </row>
     <row r="4">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Refreshed 2026-09-10 from the per-row result files, not from any roll-up. Every column is the full 5,349 validation questions. Scorer docvqa_anls_v1 — one matcher for all six: the two runners added 2026-09-10 import it from docvqa_eval_core.py, and it is a verbatim copy of what the four earlier standalone runners each carried, so the columns are comparable. ANLS takes the max over each question's answer list, threshold 0.5.</t>
+          <t>Refreshed 2026-09-11 from the per-row result files, not from any roll-up. Every column is the full 5,349 validation questions. TWO NUMBERS PER COLUMN AND THEY DIFFER IN KIND: ANLS is the reported metric and is graded, taking the max over each question's answer list with the official 0.5 threshold; Overall accuracy is a binary column this project added, now at scorer docvqa_lenient_v2. ANLS was not affected by the rescore — it never had the problem. The v2 matcher added two branches on 2026-09-11 (+323 rows across six models) and refused three fuzzy ones; the measurements are on the benchmark's scoring page.</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>DOCVQA_Gemini_Flash3.5lite_Google, 5,349 rows, accuracy 0.9602, ANLS 0.9394. Native Google AI Studio route, thinking_budget=128, max_output_tokens=8192, seed=42 — the same config as its MMLU column. FIVE ROWS ARE PERMANENTLY EMPTY: finish_reason MALFORMED_RESPONSE, thought tokens spent and no output part, reproducible at the same seed. They are scored 0. 5 of 5,349 is 0.09%.</t>
+          <t>DOCVQA_Gemini_Flash3.5lite_Google, 5,349 rows, accuracy 0.9686, ANLS 0.9394. Native Google AI Studio route, thinking_budget=128, max_output_tokens=8192, seed=42 — the same config as its MMLU column. FIVE ROWS ARE PERMANENTLY EMPTY: finish_reason MALFORMED_RESPONSE, thought tokens spent and no output part, reproducible at the same seed. They are scored 0. 5 of 5,349 is 0.09%.</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>DOCVQA_GPT_5.6_Luna, 5,349 rows, accuracy 0.9151, ANLS 0.8635, 0 empty. max_completion_tokens=16384, reasoning_effort=low, seed=42 — the same config as its MMLU and bbh columns. Run as 5 shards with a 2.5 s sleep, which is the fix from the daily-cap incident in OPENAI_EVAL_NOTES.md, not a preference.</t>
+          <t>DOCVQA_GPT_5.6_Luna, 5,349 rows, accuracy 0.9288, ANLS 0.8635, 0 empty. max_completion_tokens=16384, reasoning_effort=low, seed=42 — the same config as its MMLU and bbh columns. Run as 5 shards with a 2.5 s sleep, which is the fix from the daily-cap incident in OPENAI_EVAL_NOTES.md, not a preference.</t>
         </is>
       </c>
     </row>
